--- a/out/Attention_Base_repeat_1_000001.xlsx
+++ b/out/Attention_Base_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.832148338784464e-06</v>
+        <v>-6.091669557068963e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.004232556441540479</v>
+        <v>0.02622896046273935</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.008477399585968349</v>
+        <v>0.05252791908624256</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.01635559466203794</v>
+        <v>0.1013355181615279</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.03696752685453533</v>
+        <v>0.2290387254848797</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.005028322692181141</v>
+        <v>0.03117188245598751</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.03064998499724956</v>
+        <v>0.1899170331712018</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.001016518018286126</v>
+        <v>0.006324195006054468</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02764779603209684</v>
+        <v>0.1713455871129997</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0008799028114871704</v>
+        <v>0.005475526716775316</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.0283897670250315</v>
+        <v>0.1759668516363937</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0004276109557171406</v>
+        <v>0.002673967843898862</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.02836417343407613</v>
+        <v>0.1758343087159102</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0002014650278321249</v>
+        <v>0.001273880463659181</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.02833903618857206</v>
+        <v>0.1757045750981274</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>8.073337126826326e-05</v>
+        <v>0.0005277716643099216</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.02829935820691299</v>
+        <v>0.1754847696973214</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>5.441870473201139e-05</v>
+        <v>0.0003638589722324863</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>11.27907012395075</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.02832759983743518</v>
+        <v>0.1756850060135536</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>2.012719392291053e-05</v>
+        <v>0.0001489845986557851</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.02831259841806861</v>
+        <v>0.1756185877265909</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>7.695260611036803e-06</v>
+        <v>7.518059333286401e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.0283085044299718</v>
+        <v>0.1756191588757692</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.486408645023248e-07</v>
+        <v>2.649184518701395e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.02830062255448615</v>
+        <v>0.1755968676228551</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-2.136833693320556e-06</v>
+        <v>1.217899784007667e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.0282960943924546</v>
+        <v>0.1755946986506656</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.87065653562344e-06</v>
+        <v>3.470075982824195e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.103979445500941</v>
+        <v>11.27907012395075</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.02829105198503309</v>
+        <v>0.1755894403782135</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.467174384402158e-06</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.02828595509418635</v>
+        <v>0.1755839534485529</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.538828146730642e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.02828081046286051</v>
+        <v>0.1755783749232499</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.1755731814285158</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.02828053147455433</v>
+        <v>0.1755678536341931</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.1755678934896653</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.028280611185499</v>
+        <v>0.1755679333451376</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.02828060321440454</v>
+        <v>0.1755679253740432</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.1755680847959323</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.02828101771131647</v>
+        <v>0.1755683398709551</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1755680927670267</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.02828073075191584</v>
+        <v>0.1755680529115545</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1755680608826489</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1755680927670267</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.0282808662605217</v>
+        <v>0.1755681884201604</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.02828080249176605</v>
+        <v>0.1755681246514046</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.1755680847959323</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1755680608826489</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.02828049161908205</v>
+        <v>0.1755678137787208</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.02828041190813749</v>
+        <v>0.175567734067776</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.02828045973470423</v>
+        <v>0.1755677818943427</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.02828057930112118</v>
+        <v>0.1755679014607598</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.02828056335893215</v>
+        <v>0.1755678855185709</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.02828057930112118</v>
+        <v>0.1755679014607598</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.02828056335893215</v>
+        <v>0.1755678855185709</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1755679413162321</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1755679413162321</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1755679413162321</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1755680927670267</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.02828098582693865</v>
+        <v>0.1755683079865773</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.02828089814489952</v>
+        <v>0.1755682203045383</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.02828085031833278</v>
+        <v>0.1755681724779715</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.02828089814489952</v>
+        <v>0.1755682203045383</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02828071480972692</v>
+        <v>0.1755680369693655</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02828072278082138</v>
+        <v>0.17556804494046</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02828073075191584</v>
+        <v>0.1755680529115545</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1755680608826489</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1755680608826489</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02828077857848268</v>
+        <v>0.1755681007381212</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.02828084234723833</v>
+        <v>0.1755681645068771</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.02828095394256082</v>
+        <v>0.1755682761021994</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02828100176912756</v>
+        <v>0.1755683239287662</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02828096191365528</v>
+        <v>0.1755682840732939</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02828089017380506</v>
+        <v>0.1755682123334438</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02828100974022201</v>
+        <v>0.1755683318998607</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02828085031833278</v>
+        <v>0.1755681724779715</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1755679413162321</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.1755678934896653</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.02828060321440454</v>
+        <v>0.1755679253740432</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.02828058727221563</v>
+        <v>0.1755679094318543</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.02828046770579868</v>
+        <v>0.1755677898654372</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.02828042785032641</v>
+        <v>0.1755677500099649</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.1755678934896653</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.02828070683863247</v>
+        <v>0.1755680289982711</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.02828069089644356</v>
+        <v>0.1755680130560822</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.02828062712768791</v>
+        <v>0.1755679492873266</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.02828052350345987</v>
+        <v>0.1755678456630986</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.02828040393704292</v>
+        <v>0.1755677260966816</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.02828052350345987</v>
+        <v>0.1755678456630986</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.1755678934896653</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1755679891427988</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.02828054741674324</v>
+        <v>0.175567869576382</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.02828055538783769</v>
+        <v>0.1755678775474764</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000001.xlsx
+++ b/out/Attention_Base_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5039794455009408</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5039794455009408</v>
+        <v>0.3496946894453833</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.832148338784464e-06</v>
+        <v>-5.170525801554322e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.004232556441540479</v>
+        <v>0.02226267582022598</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.008477399585968349</v>
+        <v>0.04458497980702482</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.01635559466203794</v>
+        <v>0.086012490382241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.03696752685453533</v>
+        <v>0.194405658881264</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.005028322692181141</v>
+        <v>0.02645843321460207</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.03064998499724956</v>
+        <v>0.1611994935242268</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.001016518018286126</v>
+        <v>0.005367167805596199</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02764779603209684</v>
+        <v>0.1454354493357006</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0008799028114871704</v>
+        <v>0.004646467286595588</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.0283897670250315</v>
+        <v>0.1493571847139054</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0004276109557171406</v>
+        <v>0.002269357597289628</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.02836417343407613</v>
+        <v>0.1492439184080579</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0002014650278321249</v>
+        <v>0.001080110696438093</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.02833903618857206</v>
+        <v>0.1491330519388947</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>8.073337126826326e-05</v>
+        <v>0.0004470486848690245</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.02829935820691299</v>
+        <v>0.1489456812156155</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>5.441870473201139e-05</v>
+        <v>0.0003082986249506055</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.02832759983743518</v>
+        <v>0.1491150356930171</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>2.012719392291053e-05</v>
+        <v>0.0001257902658038677</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.02831259841806861</v>
+        <v>0.1490578494854695</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>7.695260611036803e-06</v>
+        <v>6.315350433293442e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.0283085044299718</v>
+        <v>0.1490575849622709</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.486408645023248e-07</v>
+        <v>2.176806840896185e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.02830062255448615</v>
+        <v>0.1490378873972939</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-2.136833693320556e-06</v>
+        <v>9.315831533397223e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.0282960943924546</v>
+        <v>0.1490352944137028</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.87065653562344e-06</v>
+        <v>2.340732518447637e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.02829105198503309</v>
+        <v>0.1490300705775777</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.467174384402158e-06</v>
+        <v>-1.80304630641295e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.02828595509418635</v>
+        <v>0.1490246486543859</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.538828146730642e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.02828081046286051</v>
+        <v>0.1490191430205586</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.1490139495258245</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.02828053147455433</v>
+        <v>0.1490086217315018</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.149008661586974</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.028280611185499</v>
+        <v>0.1490087014424463</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.02828060321440454</v>
+        <v>0.1490086934713519</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.149008852893241</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.02828101771131647</v>
+        <v>0.1490091079682638</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1490088608643354</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.02828073075191584</v>
+        <v>0.1490088210088632</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1490088289799576</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1490088608643354</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.0282808662605217</v>
+        <v>0.1490089565174691</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.02828080249176605</v>
+        <v>0.1490088927487133</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.02828076263629377</v>
+        <v>0.149008852893241</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1490088289799576</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.02828049161908205</v>
+        <v>0.1490085818760295</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.02828041190813749</v>
+        <v>0.1490085021650847</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.02828045973470423</v>
+        <v>0.1490085499916514</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.02828057930112118</v>
+        <v>0.1490086695580685</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.02828056335893215</v>
+        <v>0.1490086536158796</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.02828057930112118</v>
+        <v>0.1490086695580685</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.02828056335893215</v>
+        <v>0.1490086536158796</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1490087094135408</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1490087094135408</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1490087094135408</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.02828077060738823</v>
+        <v>0.1490088608643354</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.02828098582693865</v>
+        <v>0.149009076083886</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.02828089814489952</v>
+        <v>0.149008988401847</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.02828085031833278</v>
+        <v>0.1490089405752802</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.02828089814489952</v>
+        <v>0.149008988401847</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02828071480972692</v>
+        <v>0.1490088050666742</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02828072278082138</v>
+        <v>0.1490088130377687</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02828073075191584</v>
+        <v>0.1490088210088632</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1490088289799576</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.02828073872301029</v>
+        <v>0.1490088289799576</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02828077857848268</v>
+        <v>0.1490088688354299</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.02828084234723833</v>
+        <v>0.1490089326041858</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.02828095394256082</v>
+        <v>0.1490090441995081</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02828100176912756</v>
+        <v>0.1490090920260749</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02828096191365528</v>
+        <v>0.1490090521706026</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02828089017380506</v>
+        <v>0.1490089804307525</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02828100974022201</v>
+        <v>0.1490090999971693</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02828085031833278</v>
+        <v>0.1490089405752802</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02828061915659346</v>
+        <v>0.1490087094135408</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.149008661586974</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.02828060321440454</v>
+        <v>0.1490086934713519</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.02828058727221563</v>
+        <v>0.149008677529163</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.02828046770579868</v>
+        <v>0.1490085579627459</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.02828042785032641</v>
+        <v>0.1490085181072736</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.149008661586974</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.02828070683863247</v>
+        <v>0.1490087970955798</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.02828069089644356</v>
+        <v>0.1490087811533909</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.02828062712768791</v>
+        <v>0.1490087173846352</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.02828052350345987</v>
+        <v>0.1490086137604073</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.02828040393704292</v>
+        <v>0.1490084941939903</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.02828052350345987</v>
+        <v>0.1490086137604073</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.02828057133002661</v>
+        <v>0.149008661586974</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.02828066698316019</v>
+        <v>0.1490087572401075</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.02828054741674324</v>
+        <v>0.1490086376736907</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.02828055538783769</v>
+        <v>0.1490086456447851</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000001.xlsx
+++ b/out/Attention_Base_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.007402433082461357</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.001666146330535412</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.002309865318238735</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003460902720689774</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.003498265519738197</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.83168445073744</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0007694996893405914</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.83168445073744</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.002307677641510963</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.83168445073744</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00355851836502552</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.83168445073744</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.003916643559932709</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.83168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005076304078102112</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.63168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.005283433943986893</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.63168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006009660661220551</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.63168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.005893655121326447</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.63168445073744</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004929114133119583</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.63168445073744</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003641638904809952</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002295664511620998</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001718353480100632</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.00133275892585516</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0009901914745569229</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001102966256439686</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001231047324836254</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001051673665642738</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0005236044526100159</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0001270361244678497</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-2.834107726812363e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0001052916049957275</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-7.167737931013107e-05</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0002296864986419678</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0003197537735104561</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0003876779228448868</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0003834376111626625</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0006739553064107895</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0003968691453337669</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-9.903032332658768e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0002894364297389984</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0004543960094451904</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0005413535982370377</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0005470588803291321</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0001520905643701553</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006068311631679535</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3496946894453833</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001608683727681637</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.003270972985774279</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-5.170525801554322e-05</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.02226267582022598</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.004310641437768936</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.04458497980702482</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.086012490382241</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.008198635652661324</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.194405658881264</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.02645843321460207</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01269891858100891</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1611994935242268</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.005367167805596199</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01401931419968605</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1454354493357006</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.004646467286595588</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01975078321993351</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1493571847139054</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.002269357597289628</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01912679523229599</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1492439184080579</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001080110696438093</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.02104137279093266</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1491330519388947</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0004470486848690245</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.02123218029737473</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1489456812156155</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0003082986249506055</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.02300756052136421</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1491150356930171</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001257902658038677</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.02000627666711807</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1490578494854695</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>6.315350433293442e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.02014506421983242</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1490575849622709</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.176806840896185e-05</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02314751408994198</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1490378873972939</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.315831533397223e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.02343115210533142</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1490352944137028</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.340732518447637e-06</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.02503862604498863</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1490300705775777</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-1.80304630641295e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02363290265202522</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1490246486543859</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.616484440191926e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.02270943485200405</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1490191430205586</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0222170278429985</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1490139495258245</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02059835381805897</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02041863277554512</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1490086217315018</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01986579596996307</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.149008661586974</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02085975930094719</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1490087014424463</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01991716399788857</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1490086934713519</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02090548351407051</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.149008852893241</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01942571066319942</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02154931426048279</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1490091079682638</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02143710106611252</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1490088608643354</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02085371315479279</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1490088210088632</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02189068496227264</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02170989848673344</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1490088289799576</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02101341262459755</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01713956706225872</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1490088608643354</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02054082974791527</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1490089565174691</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0227850005030632</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1490088927487133</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02324428036808968</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.149008852893241</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02101527154445648</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1490088289799576</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02088223397731781</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1490085818760295</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02113854140043259</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1490085021650847</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02103675156831741</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1490085499916514</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02156409434974194</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1490086695580685</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02064125426113605</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1490086536158796</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02055124752223492</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1490086695580685</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02025653794407845</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1490086536158796</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02045496180653572</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1490087094135408</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0208885483443737</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1490087094135408</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01882616057991982</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1490087094135408</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02088271826505661</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1490088608643354</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01901011541485786</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.149009076083886</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02137188240885735</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.149008988401847</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02105437777936459</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1490089405752802</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02010905370116234</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.149008988401847</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02039487659931183</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1490088050666742</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02017141319811344</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1490088130377687</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01961103081703186</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1490088210088632</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.02010451629757881</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1490088289799576</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01983597129583359</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1490088289799576</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01805310696363449</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1490088688354299</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01893807761371136</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1490089326041858</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01912546157836914</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1490090441995081</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02002002485096455</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1490090920260749</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01909476704895496</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1490090521706026</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01895385049283504</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1490089804307525</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01883799582719803</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1490090999971693</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01744545623660088</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1490089405752802</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01792551949620247</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1490087094135408</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01775152608752251</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.149008661586974</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01845969259738922</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1490086934713519</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01794926449656487</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01822148635983467</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01767800748348236</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.149008677529163</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01680735871195793</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1490085579627459</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01692213863134384</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1490085181072736</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01697012782096863</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.149008661586974</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.01745173707604408</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1490087970955798</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01759665086865425</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1490087811533909</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01698624156415462</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01653746888041496</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1490087173846352</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01530181244015694</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1490086137604073</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01487664319574833</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1490084941939903</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01602695882320404</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1490086137604073</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01587680727243423</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.149008661586974</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01642092317342758</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1490087572401075</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0158358495682478</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1490086376736907</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01506935991346836</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1490086456447851</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>
